--- a/data/CV_masterfile.xlsx
+++ b/data/CV_masterfile.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://monashuni-my.sharepoint.com/personal/helen_stoelting_monash_edu/Documents/Admin/CVs/Shiny_CV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="226" documentId="8_{B5B9EDA1-CDD6-4DF4-8E0D-B5C63F99F472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0D55AE4-E9D7-4FEF-AB01-90112753EE8C}"/>
+  <xr:revisionPtr revIDLastSave="629" documentId="8_{B5B9EDA1-CDD6-4DF4-8E0D-B5C63F99F472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0CD77EE-E1F2-4B62-80BB-48E61E07700E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{6EB03849-2AF8-48BF-8CB0-8DA445E8DC9D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{6EB03849-2AF8-48BF-8CB0-8DA445E8DC9D}"/>
   </bookViews>
   <sheets>
     <sheet name="Experience" sheetId="1" r:id="rId1"/>
     <sheet name="Education" sheetId="2" r:id="rId2"/>
+    <sheet name="Employment" sheetId="3" r:id="rId3"/>
+    <sheet name="Conferences" sheetId="4" r:id="rId4"/>
+    <sheet name="Prizes" sheetId="5" r:id="rId5"/>
+    <sheet name="Skills" sheetId="6" r:id="rId6"/>
+    <sheet name="Commitment" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="358">
   <si>
     <t>Type</t>
   </si>
@@ -178,9 +183,6 @@
   </si>
   <si>
     <t>07/2016</t>
-  </si>
-  <si>
-    <t>doi.org/10.1038/s41467-026-74195-6;doi.org/10.1016/j.molmet.2024.102064;doi.org/10.1128/mmbr.00171-22</t>
   </si>
   <si>
     <t>doi.org/10.1126/sciimmunol.adk1673;doi.org/10.1111/all.70107;doi.org/10.1016/j.jaci.2025.08.030;doi.org/10.1016/j.it.2022.05.002;doi.org/10.1172/JCI173676;doi.org/10.1038/s41385-022-00545-4</t>
@@ -312,13 +314,839 @@
   </si>
   <si>
     <t>Excellent (1.3), Overall; Very Good (1.0), Thesis</t>
+  </si>
+  <si>
+    <t>Research Fellow</t>
+  </si>
+  <si>
+    <t>Employer</t>
+  </si>
+  <si>
+    <t>10/2013</t>
+  </si>
+  <si>
+    <t>Prof Ana Traven and A/Prof Adam Rose</t>
+  </si>
+  <si>
+    <t>Biomedicine Discovery Institute, Department of Biochemistry and Molecular Biology, Monash University, Melbourne, Australia</t>
+  </si>
+  <si>
+    <t>Postdoctoral Research Associate</t>
+  </si>
+  <si>
+    <t>Inflammation, Repair and Development Section, National Heart and Lung Institute, Imperial College London, United Kingdom</t>
+  </si>
+  <si>
+    <t>03/2023</t>
+  </si>
+  <si>
+    <t>Prof Clare Lloyd</t>
+  </si>
+  <si>
+    <t>Monash_University_logo.svg</t>
+  </si>
+  <si>
+    <t>Research Assistant</t>
+  </si>
+  <si>
+    <t>01/2023</t>
+  </si>
+  <si>
+    <t>Intern (paid)</t>
+  </si>
+  <si>
+    <t>Protein Technologies, Lead Discovery Berlin, Bayer AG, Germany</t>
+  </si>
+  <si>
+    <t>Dr Joerg Weiske</t>
+  </si>
+  <si>
+    <t>Logo_Bayer.svg</t>
+  </si>
+  <si>
+    <t>University Hospital Bonn, University of Bonn, Germany</t>
+  </si>
+  <si>
+    <t>01/2015</t>
+  </si>
+  <si>
+    <t>Prof Dr Ganschow</t>
+  </si>
+  <si>
+    <t>08/2015</t>
+  </si>
+  <si>
+    <t>UKB-Logo-2017.svg</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Additional Notes</t>
+  </si>
+  <si>
+    <t>ASI VIC-TAS Branch Meeting 2026</t>
+  </si>
+  <si>
+    <t>Melbourne, Australia</t>
+  </si>
+  <si>
+    <t>Oral Presentation</t>
+  </si>
+  <si>
+    <t>Monash Biomedicine Discovery Institute ‘Metabolism, Diabetes and Obesity Program’ Research Exchange Seminar</t>
+  </si>
+  <si>
+    <t>Invited Speaker</t>
+  </si>
+  <si>
+    <t>16th Lorne Infection and Immunity 2026</t>
+  </si>
+  <si>
+    <t>Lorne, Australia</t>
+  </si>
+  <si>
+    <t>Poster Presentation</t>
+  </si>
+  <si>
+    <t>VIIN Young Investigator Symposium 2025</t>
+  </si>
+  <si>
+    <t>Organising Committee, Judge</t>
+  </si>
+  <si>
+    <t>Monash Biochemistry Student Symposium</t>
+  </si>
+  <si>
+    <t>ECR Panel Member, Judge</t>
+  </si>
+  <si>
+    <t>ASI Immunometabolism SIG Event 2025</t>
+  </si>
+  <si>
+    <t>Monash ImmuMon 2025 (Immunology at Monash)</t>
+  </si>
+  <si>
+    <t>Judge</t>
+  </si>
+  <si>
+    <t>VIIN Young Investigator Symposium</t>
+  </si>
+  <si>
+    <t>Oral Presentation, Judge</t>
+  </si>
+  <si>
+    <t>Monash Mucosal Immunology Research Group Seminar</t>
+  </si>
+  <si>
+    <t>Biomolecular Horizons 2024</t>
+  </si>
+  <si>
+    <t>Abstract published</t>
+  </si>
+  <si>
+    <t>Monash ImmuMon (Immunology at Monash)</t>
+  </si>
+  <si>
+    <t>BSI Congress 2022</t>
+  </si>
+  <si>
+    <t>CIPP XXI: 21st International Congress on Pediatric Pulmonology</t>
+  </si>
+  <si>
+    <t>Virtual</t>
+  </si>
+  <si>
+    <t>EAACI Immunology Winter School on Basic Immunology Research in Allergy and Clinical Immunology</t>
+  </si>
+  <si>
+    <t>BSI Congress 2021</t>
+  </si>
+  <si>
+    <t>ERS International Congress 2021</t>
+  </si>
+  <si>
+    <t>E-poster</t>
+  </si>
+  <si>
+    <t>E-poster, 3 min Live Presentation, Poster Session Co-chair</t>
+  </si>
+  <si>
+    <t>Keystone eSymposium Asthma: New Discoveries and Therapies in the Age of COVID</t>
+  </si>
+  <si>
+    <t>SciTalk, Poster Presentation</t>
+  </si>
+  <si>
+    <t>Chamonix, France</t>
+  </si>
+  <si>
+    <t>BSI Congress 2019</t>
+  </si>
+  <si>
+    <t>BSI London Immunology Group “Barrier Immunity” Meeting</t>
+  </si>
+  <si>
+    <t>Attendee</t>
+  </si>
+  <si>
+    <t>BSI London Immunology Group “Immunological Cross-Talk” Meeting</t>
+  </si>
+  <si>
+    <t>Liverpool, United Kingdom</t>
+  </si>
+  <si>
+    <t>Edinburgh, United Kingdom</t>
+  </si>
+  <si>
+    <t>London, United Kingdom</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>07/2026</t>
+  </si>
+  <si>
+    <t>06/2026</t>
+  </si>
+  <si>
+    <t>02/2026</t>
+  </si>
+  <si>
+    <t>11/2025</t>
+  </si>
+  <si>
+    <t>10/2025</t>
+  </si>
+  <si>
+    <t>11/2024</t>
+  </si>
+  <si>
+    <t>09/2024</t>
+  </si>
+  <si>
+    <t>07/2022</t>
+  </si>
+  <si>
+    <t>01/2022</t>
+  </si>
+  <si>
+    <t>12/2021</t>
+  </si>
+  <si>
+    <t>09/2021</t>
+  </si>
+  <si>
+    <t>03/2021</t>
+  </si>
+  <si>
+    <t>12/2020</t>
+  </si>
+  <si>
+    <t>01/2020</t>
+  </si>
+  <si>
+    <t>12/2019</t>
+  </si>
+  <si>
+    <t>09/2019</t>
+  </si>
+  <si>
+    <t>12/2018</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>ASI Postdoctoral Travel Award</t>
+  </si>
+  <si>
+    <t>AUD 5,000</t>
+  </si>
+  <si>
+    <t>Fungal Infection Trust Geoff Scott Travel Grant</t>
+  </si>
+  <si>
+    <t>Travel Grant</t>
+  </si>
+  <si>
+    <t>GBP 1,200</t>
+  </si>
+  <si>
+    <t>Monash Faculty of Medicine, Nursing and Health Sciences Platform Access Grant</t>
+  </si>
+  <si>
+    <t>AUD 14,936</t>
+  </si>
+  <si>
+    <t>Runner Up – Best Oral Presentation</t>
+  </si>
+  <si>
+    <t>AUD 200</t>
+  </si>
+  <si>
+    <t>AUD 500</t>
+  </si>
+  <si>
+    <t>Imperial College Trust Conference Funding</t>
+  </si>
+  <si>
+    <t>GBP 400</t>
+  </si>
+  <si>
+    <t>Cayman Chemical Conference Grant</t>
+  </si>
+  <si>
+    <t>USD 250</t>
+  </si>
+  <si>
+    <t>BSI Congress 2022 Travel Bursary</t>
+  </si>
+  <si>
+    <t>GBP 250</t>
+  </si>
+  <si>
+    <t>Imperial College London Graduate School Science Writing Competition</t>
+  </si>
+  <si>
+    <t>Joint 3rd Prize (Entry: “If Dr. Seuss wrote my PhD”)</t>
+  </si>
+  <si>
+    <t>GBP 150</t>
+  </si>
+  <si>
+    <t>EAACI Winter School</t>
+  </si>
+  <si>
+    <t>Best Oral Presentation</t>
+  </si>
+  <si>
+    <t>CHF 150</t>
+  </si>
+  <si>
+    <t>BSI Congress 2021 Travel Bursary</t>
+  </si>
+  <si>
+    <t>ERS Lung Science Conference Bursary</t>
+  </si>
+  <si>
+    <t>Conference Bursary</t>
+  </si>
+  <si>
+    <t>12-week Stipend Extension</t>
+  </si>
+  <si>
+    <t>GBP 5,997</t>
+  </si>
+  <si>
+    <t>Keystone eSymposia Trainee Scholarship</t>
+  </si>
+  <si>
+    <t>Scholarship</t>
+  </si>
+  <si>
+    <t>BSI Congress 2019 Travel Bursary</t>
+  </si>
+  <si>
+    <t>British Lung Foundation PhD Stipend</t>
+  </si>
+  <si>
+    <t>GBP 72,428</t>
+  </si>
+  <si>
+    <t>MSc Immunology Dean’s Prize</t>
+  </si>
+  <si>
+    <t>GBP 200</t>
+  </si>
+  <si>
+    <t>German Academic Exchange Service (DAAD) RISE Worldwide</t>
+  </si>
+  <si>
+    <t>EUR 1,575</t>
+  </si>
+  <si>
+    <t>2024 ICB Cover Competition for Immunology &amp; Cell Biology</t>
+  </si>
+  <si>
+    <t>09/2025</t>
+  </si>
+  <si>
+    <t>03/2024</t>
+  </si>
+  <si>
+    <t>06/2022</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>“Using cutting edge multi-omics approaches to shed light on exacerbated fungal disease in diabetes”</t>
+  </si>
+  <si>
+    <t>Research Grant</t>
+  </si>
+  <si>
+    <t>Presentation Prize</t>
+  </si>
+  <si>
+    <t>08/2026</t>
+  </si>
+  <si>
+    <t>ASI Snapshot Image Competition</t>
+  </si>
+  <si>
+    <t>non-monetary</t>
+  </si>
+  <si>
+    <t>Competition</t>
+  </si>
+  <si>
+    <t>Award</t>
+  </si>
+  <si>
+    <t>Free registration</t>
+  </si>
+  <si>
+    <t>equal to EUR 89</t>
+  </si>
+  <si>
+    <t>equal to USD 150</t>
+  </si>
+  <si>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>ICB Cover.jpg</t>
+  </si>
+  <si>
+    <t>Snapshot.png</t>
+  </si>
+  <si>
+    <t>Imperial College London</t>
+  </si>
+  <si>
+    <t>Primary image for ASI 'Day of Immunology 2027' marketing campaign</t>
+  </si>
+  <si>
+    <t>Cover of Immunology &amp; Cell Biology since 2024</t>
+  </si>
+  <si>
+    <t>Best Overall Performance</t>
+  </si>
+  <si>
+    <t>PhD Studentship</t>
+  </si>
+  <si>
+    <t>In support of a 2-month internship at Roehampton University, United Kingdom</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>UK Home Office PIL A, B and C holder</t>
+  </si>
+  <si>
+    <t>Mouse breeding and colony management of transgenics</t>
+  </si>
+  <si>
+    <t>Lung function measurements (Scireq flexiVent)</t>
+  </si>
+  <si>
+    <t>Cannulation of trachea, bronchoalveolar lavage and in situ inflation of lungs</t>
+  </si>
+  <si>
+    <t>Dissection (neonatal and adult mice), perfusion, cardiac puncture</t>
+  </si>
+  <si>
+    <t>Generation of precision-cut lung slices (PCLS)</t>
+  </si>
+  <si>
+    <t>Cell transfection, viral transduction, generation of KO cell lines using CRISPR/Cas9</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>Nucleic acid isolation, (q)PCR, ELISA, western blot</t>
+  </si>
+  <si>
+    <t>Bacterial and fungal culture and molecular cloning</t>
+  </si>
+  <si>
+    <t>Protein expression and purification, thermal shift assay</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Adobe Illustrator</t>
+  </si>
+  <si>
+    <t>FlowJo</t>
+  </si>
+  <si>
+    <t>ImageJ</t>
+  </si>
+  <si>
+    <t>Imaris</t>
+  </si>
+  <si>
+    <t>QuPath</t>
+  </si>
+  <si>
+    <t>MS Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulk RNA sequencing analysis </t>
+  </si>
+  <si>
+    <t>Analysis of large datasets, including omics</t>
+  </si>
+  <si>
+    <t>Animal Ethics (gaining approval and reporting)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administration methods in mice: Intranasal, intraperitoneal, intravenous and oral gavage </t>
+  </si>
+  <si>
+    <t>Infection with viral, bacterial and fungal pathogens (including class 2 pathogens)</t>
+  </si>
+  <si>
+    <t>Analysis</t>
+  </si>
+  <si>
+    <t>Reproducible and automated analysis using Rstudio</t>
+  </si>
+  <si>
+    <t>Automated image analysis</t>
+  </si>
+  <si>
+    <t>CellProfiler</t>
+  </si>
+  <si>
+    <t>IntegratedGeneViewer</t>
+  </si>
+  <si>
+    <t>Use of High-Performance Computing (HPC) resources</t>
+  </si>
+  <si>
+    <t>Shiny</t>
+  </si>
+  <si>
+    <t>Biochemical assays</t>
+  </si>
+  <si>
+    <t>Microscopy: basic, confocal, live imaging, second-harmonics generation</t>
+  </si>
+  <si>
+    <t>IHC and immunofluorescence</t>
+  </si>
+  <si>
+    <t>Flow cytometry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouse models of allergic airway disease and invasive fungal infection with Candida sp. </t>
+  </si>
+  <si>
+    <t>Bone marrow isolation</t>
+  </si>
+  <si>
+    <t>German (native)</t>
+  </si>
+  <si>
+    <t>French (conversational)</t>
+  </si>
+  <si>
+    <t>English (fluent)</t>
+  </si>
+  <si>
+    <t>Latin (proficiency certificate)</t>
+  </si>
+  <si>
+    <t>ASI VIC TAS 2026.png</t>
+  </si>
+  <si>
+    <t>BDI.png</t>
+  </si>
+  <si>
+    <t>Lorne 2026.png</t>
+  </si>
+  <si>
+    <t>Immunometabolism 2025.png</t>
+  </si>
+  <si>
+    <t>VIIN.svg</t>
+  </si>
+  <si>
+    <t>BSS.png</t>
+  </si>
+  <si>
+    <t>Immumon 2025.png</t>
+  </si>
+  <si>
+    <t>MIRG.png</t>
+  </si>
+  <si>
+    <t>BMH24.png</t>
+  </si>
+  <si>
+    <t>Immumon 2024.png</t>
+  </si>
+  <si>
+    <t>BSI 2022.jpg</t>
+  </si>
+  <si>
+    <t>CIPP XXI.png</t>
+  </si>
+  <si>
+    <t>Winter_school_logo.png</t>
+  </si>
+  <si>
+    <t>BSI 2021.png</t>
+  </si>
+  <si>
+    <t>ERS 2021.png</t>
+  </si>
+  <si>
+    <t>ERS Lung Science Conference 2021</t>
+  </si>
+  <si>
+    <t>EAACI Immunology Winter School on Basic Immunology Research in Allergy and Clinical Immunology 2022</t>
+  </si>
+  <si>
+    <t>LSC 2021.jpg</t>
+  </si>
+  <si>
+    <t>Keystone 2021.png</t>
+  </si>
+  <si>
+    <t>BSI 2019.jpg</t>
+  </si>
+  <si>
+    <t>LIG.jpg</t>
+  </si>
+  <si>
+    <t>12/2017</t>
+  </si>
+  <si>
+    <t>BSI Congress 2017</t>
+  </si>
+  <si>
+    <t>Brighton, United Kingdom</t>
+  </si>
+  <si>
+    <t>BSI 2017.jpg</t>
+  </si>
+  <si>
+    <t>in vivo.png</t>
+  </si>
+  <si>
+    <t>general.svg</t>
+  </si>
+  <si>
+    <t>analysis.svg</t>
+  </si>
+  <si>
+    <t>software.svg</t>
+  </si>
+  <si>
+    <t>in vitro.svg</t>
+  </si>
+  <si>
+    <t>languages.svg</t>
+  </si>
+  <si>
+    <t>Languages</t>
+  </si>
+  <si>
+    <t>In vivo</t>
+  </si>
+  <si>
+    <t>In vitro</t>
+  </si>
+  <si>
+    <t>Logo_Charite.svg</t>
+  </si>
+  <si>
+    <t>Roehampton.png</t>
+  </si>
+  <si>
+    <t>doi.org/10.1038/s41564-026-02454-9;doi.org/10.1038/s41467-026-74195-6;doi.org/10.1016/j.molmet.2024.102064;doi.org/10.1128/mmbr.00171-22</t>
+  </si>
+  <si>
+    <t>Cell culture of human and mouse primary cells and cell lines</t>
+  </si>
+  <si>
+    <t>Air-liquid interface (ALI) culture of primary airway epithelial cells</t>
+  </si>
+  <si>
+    <t>Public Engagement</t>
+  </si>
+  <si>
+    <t>"Injecting hope: the race for a COVID-19 vaccine" Origami activity organised by British Society for Immunology</t>
+  </si>
+  <si>
+    <t>Science Museum Lates, London, United Kingdom</t>
+  </si>
+  <si>
+    <t>Short profile in Breathing Together Play and Learn Activity Guide</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>http://breathingtogether.co.uk/activity-guide/</t>
+  </si>
+  <si>
+    <t>Breathing Together 'Under Fives' Training Workshop</t>
+  </si>
+  <si>
+    <t>Strategies for communicating science to children, London, United Kingdom</t>
+  </si>
+  <si>
+    <t>10/2019</t>
+  </si>
+  <si>
+    <t>06/2019</t>
+  </si>
+  <si>
+    <t>"WHOOSH-CRACKLE-POP!" 0-3s Play Space hosted by Breathing Together</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great Exhibition Road Festival, London, United Kingdom </t>
+  </si>
+  <si>
+    <t>04/2018</t>
+  </si>
+  <si>
+    <t>Breathing Together 0-12s Live Family Event</t>
+  </si>
+  <si>
+    <t>Imperial Festival, London, United Kingdom</t>
+  </si>
+  <si>
+    <t>Committees</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>since 2025</t>
+  </si>
+  <si>
+    <t>Monash BDI ECR Committee  · Mentoring Subcommittee Chair (2026), Member (2025-Present)</t>
+  </si>
+  <si>
+    <t>VIIN Emerging Leaders Committee  · Sponsoring Subcommittee (2026) &amp; Workshops Subcommittee (2025)</t>
+  </si>
+  <si>
+    <t>Leading a small team to facilitate the BDI's flagship mentoring program, scaling participant intake by over 24% while overseeing mentee training and mentor orientation session to support ECR career development;Evaluated and scored competitive applications for the BDI ECR Development Prize as part of broader committee governance</t>
+  </si>
+  <si>
+    <t>Spearheaded sponsorship outreach for 2026, single-handedly securing $3,400 of the team's $6,400 total (a 570%+ increase compared to the previous year's total raised);Co-organised the successful "How to Get a Grant" online workshop and actively delivered core operations for the annual Young Investigator Symposium, including abstract review, presentation judging and event logistics</t>
+  </si>
+  <si>
+    <t>Bullets</t>
+  </si>
+  <si>
+    <t>Peer review</t>
+  </si>
+  <si>
+    <t>since 2019</t>
+  </si>
+  <si>
+    <t>Independent peer review for Nature Communications, American Journal of Respiratory and Critical Care Medicine, Microbiology Spectrum;Co-peer review for Science Immunology, Science Advances, Cell Metabolism, Mucosal Immunology</t>
+  </si>
+  <si>
+    <t>since 2024</t>
+  </si>
+  <si>
+    <t>Presentation judge</t>
+  </si>
+  <si>
+    <t>VIIN Young Investigator Symposium 2025;Monash Biochemistry Student Symposium 2025; Monash ImmuMon 2025; VIIN Young Investigator Symposium 2024</t>
+  </si>
+  <si>
+    <t>Day-to-day advisor to PhD student Ms Antara Ghoshal</t>
+  </si>
+  <si>
+    <t>Supervised by A/Prof Adam Rose and Prof Ana Traven</t>
+  </si>
+  <si>
+    <t>2024 and 2025</t>
+  </si>
+  <si>
+    <t>Mentor for "Experimental Design" activity</t>
+  </si>
+  <si>
+    <t>Master of Biomedical and Health Sciences, Monash University</t>
+  </si>
+  <si>
+    <t>since 2021</t>
+  </si>
+  <si>
+    <t>Chair</t>
+  </si>
+  <si>
+    <t>Sectional seminars and journal clubs (Inflammation, Development and Repair section, NHLI, Imperial College London) (2023);ERS Lung Science Conference session chair (2021)</t>
+  </si>
+  <si>
+    <t>2018-2023</t>
+  </si>
+  <si>
+    <t>Website and social media management</t>
+  </si>
+  <si>
+    <t>Lloyd lab, NHLI, Imperial College London</t>
+  </si>
+  <si>
+    <t>2019-2022</t>
+  </si>
+  <si>
+    <t>Graduate Teaching Assistant</t>
+  </si>
+  <si>
+    <t>2017-2018</t>
+  </si>
+  <si>
+    <t>Course Representative</t>
+  </si>
+  <si>
+    <t>MSc Immunology, Imperial College London</t>
+  </si>
+  <si>
+    <t>Panel Member</t>
+  </si>
+  <si>
+    <t>"Inspiring ECR" panel discussion at Monash Biochemistry Student Symposium</t>
+  </si>
+  <si>
+    <t>German Society for Immunology (DGfI) – since 2025;Australian Society for Microbiology (ASM) – 2024-2025;Australian and New Zealand Society for Immunology (ASI) – since 2024;Victorian Infection and Immunity Network (VIIN) – since 2023;European Respiratory Society (ERS) – since 2020;British Thoracic Society (BTS) – since 2020;European Academy of Allergy and Clinical Immunology (EAACI) – since 2019;British Society for Immunology (BSI) – since 2017</t>
+  </si>
+  <si>
+    <t>Society Memberships</t>
+  </si>
+  <si>
+    <t>Teaching and Supervision</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,6 +1174,14 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -364,10 +1200,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -403,8 +1240,14 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -737,17 +1580,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC0A4288-14F4-4FCB-B84F-D8D01C24F236}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="64.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="98.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="161.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" customWidth="1"/>
+    <col min="6" max="6" width="98.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="161.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -761,16 +1604,19 @@
         <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
@@ -783,17 +1629,20 @@
       <c r="D2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>51</v>
+      <c r="E2" t="s">
+        <v>93</v>
       </c>
       <c r="F2" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="H2" s="6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>18</v>
       </c>
@@ -806,17 +1655,20 @@
       <c r="D3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>52</v>
+      <c r="E3" s="10" t="s">
+        <v>78</v>
       </c>
       <c r="F3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="H3" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -829,17 +1681,20 @@
       <c r="D4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>49</v>
+      <c r="E4" s="10" t="s">
+        <v>78</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="H4" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>23</v>
       </c>
@@ -852,14 +1707,17 @@
       <c r="D5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="E5" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>23</v>
       </c>
@@ -872,14 +1730,17 @@
       <c r="D6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="E6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>23</v>
       </c>
@@ -892,17 +1753,20 @@
       <c r="D7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="E7" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>27</v>
       </c>
@@ -915,14 +1779,17 @@
       <c r="D8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="E8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -935,17 +1802,20 @@
       <c r="D9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="E9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
   </sheetData>
@@ -973,7 +1843,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -982,95 +1852,95 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" t="s">
         <v>61</v>
       </c>
-      <c r="G1" t="s">
-        <v>62</v>
-      </c>
       <c r="H1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>58</v>
-      </c>
       <c r="C2" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="C3" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>66</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>67</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="C4" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>44</v>
@@ -1079,19 +1949,1701 @@
         <v>30</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A4AE233-F544-41E6-A9A2-E47CFF04CB58}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5E4C3E-ECD4-4E72-A578-49EE37F687E1}">
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.85546875" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F12" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" t="s">
+        <v>127</v>
+      </c>
+      <c r="F13" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B15" t="s">
+        <v>285</v>
+      </c>
+      <c r="C15" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>127</v>
+      </c>
+      <c r="F15" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="B17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D17" t="s">
+        <v>135</v>
+      </c>
+      <c r="E17" t="s">
+        <v>127</v>
+      </c>
+      <c r="F17" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B18" t="s">
+        <v>284</v>
+      </c>
+      <c r="C18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" t="s">
+        <v>136</v>
+      </c>
+      <c r="E18" t="s">
+        <v>127</v>
+      </c>
+      <c r="F18" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" t="s">
+        <v>127</v>
+      </c>
+      <c r="F21" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="B22" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B23" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" t="s">
+        <v>115</v>
+      </c>
+      <c r="F23" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="B24" t="s">
+        <v>291</v>
+      </c>
+      <c r="C24" t="s">
+        <v>292</v>
+      </c>
+      <c r="D24" t="s">
+        <v>142</v>
+      </c>
+      <c r="F24" t="s">
+        <v>293</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C32E256-418F-4D73-88D3-033C6956F750}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="B2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E12" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" t="s">
+        <v>216</v>
+      </c>
+      <c r="D14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C15" t="s">
+        <v>192</v>
+      </c>
+      <c r="D15" t="s">
+        <v>195</v>
+      </c>
+      <c r="E15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" t="s">
+        <v>194</v>
+      </c>
+      <c r="C16" t="s">
+        <v>216</v>
+      </c>
+      <c r="D16" t="s">
+        <v>191</v>
+      </c>
+      <c r="E16" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" t="s">
+        <v>196</v>
+      </c>
+      <c r="D17" t="s">
+        <v>170</v>
+      </c>
+      <c r="E17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>197</v>
+      </c>
+      <c r="C18" t="s">
+        <v>226</v>
+      </c>
+      <c r="D18" t="s">
+        <v>195</v>
+      </c>
+      <c r="E18" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C19" t="s">
+        <v>225</v>
+      </c>
+      <c r="D19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>201</v>
+      </c>
+      <c r="C20" t="s">
+        <v>227</v>
+      </c>
+      <c r="D20" t="s">
+        <v>195</v>
+      </c>
+      <c r="E20" t="s">
+        <v>202</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B791D823-B9A3-4FB1-8BD6-3F1E7614E2A1}">
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="78.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>301</v>
+      </c>
+      <c r="B11" t="s">
+        <v>264</v>
+      </c>
+      <c r="C11" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>302</v>
+      </c>
+      <c r="B12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>302</v>
+      </c>
+      <c r="B13" t="s">
+        <v>307</v>
+      </c>
+      <c r="C13" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>302</v>
+      </c>
+      <c r="B14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C14" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>302</v>
+      </c>
+      <c r="B15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C15" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>236</v>
+      </c>
+      <c r="B16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C16" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" t="s">
+        <v>259</v>
+      </c>
+      <c r="C17" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B18" t="s">
+        <v>262</v>
+      </c>
+      <c r="C18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>236</v>
+      </c>
+      <c r="B19" t="s">
+        <v>261</v>
+      </c>
+      <c r="C19" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>236</v>
+      </c>
+      <c r="B20" t="s">
+        <v>260</v>
+      </c>
+      <c r="C20" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>236</v>
+      </c>
+      <c r="B21" t="s">
+        <v>237</v>
+      </c>
+      <c r="C21" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>236</v>
+      </c>
+      <c r="B22" t="s">
+        <v>239</v>
+      </c>
+      <c r="C22" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>252</v>
+      </c>
+      <c r="B23" t="s">
+        <v>253</v>
+      </c>
+      <c r="C23" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>252</v>
+      </c>
+      <c r="B24" t="s">
+        <v>247</v>
+      </c>
+      <c r="C24" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>252</v>
+      </c>
+      <c r="B25" t="s">
+        <v>248</v>
+      </c>
+      <c r="C25" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>252</v>
+      </c>
+      <c r="B26" t="s">
+        <v>257</v>
+      </c>
+      <c r="C26" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>252</v>
+      </c>
+      <c r="B27" t="s">
+        <v>254</v>
+      </c>
+      <c r="C27" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>240</v>
+      </c>
+      <c r="B28" t="s">
+        <v>241</v>
+      </c>
+      <c r="C28" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>240</v>
+      </c>
+      <c r="B29" t="s">
+        <v>255</v>
+      </c>
+      <c r="C29" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>240</v>
+      </c>
+      <c r="B30" t="s">
+        <v>242</v>
+      </c>
+      <c r="C30" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>240</v>
+      </c>
+      <c r="B31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C31" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>240</v>
+      </c>
+      <c r="B32" t="s">
+        <v>244</v>
+      </c>
+      <c r="C32" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>240</v>
+      </c>
+      <c r="B33" t="s">
+        <v>256</v>
+      </c>
+      <c r="C33" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>240</v>
+      </c>
+      <c r="B34" t="s">
+        <v>246</v>
+      </c>
+      <c r="C34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>240</v>
+      </c>
+      <c r="B35" t="s">
+        <v>245</v>
+      </c>
+      <c r="C35" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>240</v>
+      </c>
+      <c r="B36" t="s">
+        <v>258</v>
+      </c>
+      <c r="C36" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>300</v>
+      </c>
+      <c r="B37" t="s">
+        <v>265</v>
+      </c>
+      <c r="C37" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>300</v>
+      </c>
+      <c r="B38" t="s">
+        <v>267</v>
+      </c>
+      <c r="C38" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>300</v>
+      </c>
+      <c r="B39" t="s">
+        <v>266</v>
+      </c>
+      <c r="C39" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>300</v>
+      </c>
+      <c r="B40" t="s">
+        <v>268</v>
+      </c>
+      <c r="C40" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B16:B22">
+    <sortCondition ref="B16:B22"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A33F062-63AB-4258-BB2D-6AFC01AD9388}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="99" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="99" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C4" t="s">
+        <v>349</v>
+      </c>
+      <c r="E4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>324</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" t="s">
+        <v>353</v>
+      </c>
+      <c r="E7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" t="s">
+        <v>335</v>
+      </c>
+      <c r="D8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C9" t="s">
+        <v>343</v>
+      </c>
+      <c r="D9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>324</v>
+      </c>
+      <c r="B10" t="s">
+        <v>332</v>
+      </c>
+      <c r="C10" t="s">
+        <v>331</v>
+      </c>
+      <c r="D10" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>324</v>
+      </c>
+      <c r="B11" t="s">
+        <v>345</v>
+      </c>
+      <c r="C11" t="s">
+        <v>346</v>
+      </c>
+      <c r="E11" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>324</v>
+      </c>
+      <c r="B12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>308</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
+        <v>309</v>
+      </c>
+      <c r="E13" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>308</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C14" t="s">
+        <v>311</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>308</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="C15" t="s">
+        <v>314</v>
+      </c>
+      <c r="E15" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>308</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C16" t="s">
+        <v>318</v>
+      </c>
+      <c r="E16" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>308</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="C17" t="s">
+        <v>321</v>
+      </c>
+      <c r="E17" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>356</v>
+      </c>
+      <c r="D18" t="s">
+        <v>355</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F14" r:id="rId1" xr:uid="{4F9DC852-9575-4D71-B88C-F9D124430E2A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/CV_masterfile.xlsx
+++ b/data/CV_masterfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://monashuni-my.sharepoint.com/personal/helen_stoelting_monash_edu/Documents/Admin/CVs/Shiny_CV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="629" documentId="8_{B5B9EDA1-CDD6-4DF4-8E0D-B5C63F99F472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0CD77EE-E1F2-4B62-80BB-48E61E07700E}"/>
+  <xr:revisionPtr revIDLastSave="659" documentId="8_{B5B9EDA1-CDD6-4DF4-8E0D-B5C63F99F472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{221544F8-84D0-4222-A85E-299D0A54DF1E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{6EB03849-2AF8-48BF-8CB0-8DA445E8DC9D}"/>
+    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" firstSheet="2" activeTab="7" xr2:uid="{6EB03849-2AF8-48BF-8CB0-8DA445E8DC9D}"/>
   </bookViews>
   <sheets>
     <sheet name="Experience" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Prizes" sheetId="5" r:id="rId5"/>
     <sheet name="Skills" sheetId="6" r:id="rId6"/>
     <sheet name="Commitment" sheetId="7" r:id="rId7"/>
+    <sheet name="Contact" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="374">
   <si>
     <t>Type</t>
   </si>
@@ -1136,6 +1137,54 @@
   </si>
   <si>
     <t>Teaching and Supervision</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Dr Helen Stölting</t>
+  </si>
+  <si>
+    <t>helen.stoelting@monash.edu</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Prof Ana Traven</t>
+  </si>
+  <si>
+    <t>NHMRC Investigator Fellow</t>
+  </si>
+  <si>
+    <t>ana.traven@monash.edu</t>
+  </si>
+  <si>
+    <t>A/Prof Adam Rose</t>
+  </si>
+  <si>
+    <t>Head of the Nutrient Metabolism &amp; Signalling Laboratory</t>
+  </si>
+  <si>
+    <t>adam.rose@monash.edu</t>
+  </si>
+  <si>
+    <t>Department of Biochemistry and Molecular Biology;Metabolism, Diabetes and Obesity Program;Biomedicine Discovery Institute;Monash University | 23 Innovation Walk;Clayton | VIC 3800 | Australia</t>
+  </si>
+  <si>
+    <t>Department of Biochemistry and Molecular Biology;Infection Program | Metabolism, Diabetes and Obesity Program;Biomedicine Discovery Institute;Monash University | 19 Innovation Walk;Clayton | VIC 3800 | Australia</t>
+  </si>
+  <si>
+    <t>Department of Biochemistry and Molecular Biology;Infection Program;Biomedicine Discovery Institute;Monash University | 19 Innovation Walk;Clayton | VIC 3800 | Australia</t>
   </si>
 </sst>
 </file>
@@ -3646,4 +3695,90 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805B12EE-3B5F-4EF1-96D1-DE193CCF4A77}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="E2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="E3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C4" t="s">
+        <v>369</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="E4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{E6A5A10F-29DB-4267-A01A-BDDC3C06FF40}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{081602A3-D87F-4A0A-A25D-5230EA6B4BFA}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{94701970-9646-4D58-A5FE-AAE7ACE23EBD}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>